--- a/utils/monday_sprint_sprint_2024-48.xlsx
+++ b/utils/monday_sprint_sprint_2024-48.xlsx
@@ -237,7 +237,7 @@
     <t>22/08/2024</t>
   </si>
   <si>
-    <t>10/03/2026</t>
+    <t>05/03/2026</t>
   </si>
   <si>
     <t>Agosto</t>
@@ -4123,7 +4123,7 @@
         <v>138</v>
       </c>
       <c r="Q10">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="4:17" x14ac:dyDescent="0.25">
@@ -4155,7 +4155,7 @@
         <v>28</v>
       </c>
       <c r="Q11">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="4:17" x14ac:dyDescent="0.25">
@@ -4269,7 +4269,7 @@
         <v>15</v>
       </c>
       <c r="F21" s="2">
-        <v>917</v>
+        <v>920</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>105</v>
@@ -4283,7 +4283,7 @@
         <v>15</v>
       </c>
       <c r="F22" s="2">
-        <v>551</v>
+        <v>546</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>69</v>

--- a/utils/monday_sprint_sprint_2024-48.xlsx
+++ b/utils/monday_sprint_sprint_2024-48.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1086" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1087" uniqueCount="219">
   <si>
     <t>Ticket</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Equipe TI</t>
   </si>
   <si>
-    <t>Entrada Sprint</t>
+    <t>Abertura</t>
   </si>
   <si>
     <t>Encerramento</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>SLA (15 dias)</t>
+    <t>Dentro da SLA</t>
   </si>
   <si>
     <t>Semana</t>
@@ -87,7 +87,7 @@
     <t>22/10/2024</t>
   </si>
   <si>
-    <t>N/A</t>
+    <t>06/11/2024</t>
   </si>
   <si>
     <t>Implantação</t>
@@ -102,7 +102,7 @@
     <t>Outubro</t>
   </si>
   <si>
-    <t>28262</t>
+    <t>7724598636</t>
   </si>
   <si>
     <t>Preenchimento das cotas</t>
@@ -117,10 +117,7 @@
     <t>Fazendo</t>
   </si>
   <si>
-    <t>Aberto</t>
-  </si>
-  <si>
-    <t>28134</t>
+    <t>7627220745</t>
   </si>
   <si>
     <t>Bloqueio programação de moldagem</t>
@@ -129,19 +126,25 @@
     <t>14/10/2024</t>
   </si>
   <si>
+    <t>07/11/2024</t>
+  </si>
+  <si>
     <t>Semana 2</t>
   </si>
   <si>
-    <t>25807</t>
+    <t>7724603677</t>
   </si>
   <si>
     <t>Sistema para Faseamento de Vendas e Faturamento / Manutenção dos dados importados</t>
   </si>
   <si>
+    <t>27/10/2024</t>
+  </si>
+  <si>
     <t>A fazer</t>
   </si>
   <si>
-    <t>28574</t>
+    <t>7714437363</t>
   </si>
   <si>
     <t>Comissões</t>
@@ -150,19 +153,25 @@
     <t>25/10/2024</t>
   </si>
   <si>
+    <t>7724598736</t>
+  </si>
+  <si>
     <t>Consulta de PDI’s preenchidos</t>
   </si>
   <si>
-    <t>25032</t>
+    <t>7723702487</t>
   </si>
   <si>
     <t>Agendar serviço para carga da base de programação para o APP</t>
   </si>
   <si>
+    <t>7724598481</t>
+  </si>
+  <si>
     <t>Revisão de PDI’s:</t>
   </si>
   <si>
-    <t>28292</t>
+    <t>7618250621</t>
   </si>
   <si>
     <t>Correção</t>
@@ -174,43 +183,58 @@
     <t>11/10/2024</t>
   </si>
   <si>
+    <t>30/10/2024</t>
+  </si>
+  <si>
+    <t>7724598570</t>
+  </si>
+  <si>
     <t>Preenchimento dos PDI’s</t>
   </si>
   <si>
-    <t>27069</t>
+    <t>7627192239</t>
   </si>
   <si>
     <t>ATUALIZAÇÃO CALCULO COMISSÃO DA INVOICE</t>
   </si>
   <si>
+    <t>29/10/2024</t>
+  </si>
+  <si>
     <t>Impedimento</t>
   </si>
   <si>
-    <t>28589</t>
+    <t>7727789788</t>
   </si>
   <si>
     <t>PDI_CheckList - Campo Livre para observações.</t>
   </si>
   <si>
-    <t>28550</t>
+    <t>7714475306</t>
   </si>
   <si>
     <t>Inclusão de filtro por sequencia - Apontamentos de produção</t>
   </si>
   <si>
+    <t>09/11/2024</t>
+  </si>
+  <si>
     <t>Feito</t>
   </si>
   <si>
+    <t>7727864377</t>
+  </si>
+  <si>
     <t>PDI_RespostaNew - Alterna cores nas colunas da sequências.</t>
   </si>
   <si>
-    <t>28419</t>
+    <t>7714929554</t>
   </si>
   <si>
     <t>ATUALIZAÇÃO DE FLUXOS</t>
   </si>
   <si>
-    <t>27180</t>
+    <t>7724603311</t>
   </si>
   <si>
     <t>Projeto</t>
@@ -222,46 +246,154 @@
     <t>Testes</t>
   </si>
   <si>
-    <t>28477</t>
+    <t>7714919023</t>
   </si>
   <si>
     <t>VISUALIZAÇÃO DE ITENS COMERCIAIS - SETOR 610</t>
   </si>
   <si>
-    <t>28547</t>
+    <t>7714529751</t>
   </si>
   <si>
     <t>Alteração pergunta MPO Usinagem</t>
   </si>
   <si>
-    <t>28526</t>
+    <t>7714582650</t>
   </si>
   <si>
     <t>ACRESCENTAR MOTIVOS DE PARADAS</t>
   </si>
   <si>
-    <t>28395</t>
+    <t>7714936691</t>
   </si>
   <si>
     <t>Recibo Embarque - Vinculo NFe x Sequência</t>
   </si>
   <si>
-    <t>28527</t>
+    <t>05/11/2024</t>
+  </si>
+  <si>
+    <t>7714568571</t>
   </si>
   <si>
     <t>INCLUSÃO DE CPC NO GED</t>
   </si>
   <si>
-    <t>27561</t>
+    <t>7723506481</t>
+  </si>
+  <si>
+    <t>Abertura de Chamado - Criação de Cadastro de Calendário de Máquina para Cálculo de IROG</t>
+  </si>
+  <si>
+    <t>7714793064</t>
+  </si>
+  <si>
+    <t>NOVO LOCAL DE EMPRÉSTIMO</t>
+  </si>
+  <si>
+    <t>7723510711</t>
+  </si>
+  <si>
+    <t>Ajustes no sistema de ensaios destrutivos de peças seriadas</t>
+  </si>
+  <si>
+    <t>7715469086</t>
+  </si>
+  <si>
+    <t>Apontamento Inspeção</t>
+  </si>
+  <si>
+    <t>7714803653</t>
+  </si>
+  <si>
+    <t>Ajuste da tela de Check list de liberação</t>
+  </si>
+  <si>
+    <t>7714822084</t>
+  </si>
+  <si>
+    <t>Correção de importação</t>
+  </si>
+  <si>
+    <t>7723510795</t>
+  </si>
+  <si>
+    <t>Registro de inspeção</t>
+  </si>
+  <si>
+    <t>04/11/2024</t>
+  </si>
+  <si>
+    <t>7714865727</t>
+  </si>
+  <si>
+    <t>Liberar Inventários no Almoxarifado</t>
+  </si>
+  <si>
+    <t>7714834106</t>
+  </si>
+  <si>
+    <t>ACRESCENTAR COLUNAS SETOR E CABINES APLICAÇÃO APONTAMENTO ACABAMENTO</t>
+  </si>
+  <si>
+    <t>7714849689</t>
+  </si>
+  <si>
+    <t>Atualizar o banco de dados dos procedimentos de embalagem</t>
+  </si>
+  <si>
+    <t>7618265898</t>
+  </si>
+  <si>
+    <t>Altona || Sistema ERP || Exportação Requisição OSI</t>
+  </si>
+  <si>
+    <t>7714891465</t>
+  </si>
+  <si>
+    <t>REGRA FLUXO 108</t>
+  </si>
+  <si>
+    <t>7724524170</t>
+  </si>
+  <si>
+    <t>Importar Planilha Tempos da Moldagem</t>
+  </si>
+  <si>
+    <t>7724081403</t>
+  </si>
+  <si>
+    <t>PROEX Financeiro (Sinalizar Status PROEX)</t>
+  </si>
+  <si>
+    <t>7715447016</t>
+  </si>
+  <si>
+    <t>Apontamentos Manipulador Rebarbação VI</t>
+  </si>
+  <si>
+    <t>7727781581</t>
+  </si>
+  <si>
+    <t>PDI_CheckList - Botão para concluir e liberar o check list</t>
+  </si>
+  <si>
+    <t>03/11/2024</t>
+  </si>
+  <si>
+    <t>22996</t>
+  </si>
+  <si>
+    <t>Excelência Operacional</t>
   </si>
   <si>
     <t>Solicitação de serviço</t>
   </si>
   <si>
-    <t>Abertura de Chamado - Criação de Cadastro de Calendário de Máquina para Cálculo de IROG</t>
-  </si>
-  <si>
-    <t>Solicito a abertura de chamado para criação de tela de cadastro no sistema que possibilite a criação de calendário de máquinas para cálculo de IROG, segue abaixo modelo utilizado no EFACT: Conforme acordado em reunião (22/08) é necessário que haja uma funcionalidade no calendário que permita que o c</t>
+    <t>Habilitar o sistema de apontamento dos manipuladores para o acabamento</t>
+  </si>
+  <si>
+    <t>Criação de sistema que consolide as informações de operação dos equipamentos da fábrica, para cálculo de IROG (Índice de rendimento operacional global). O sistema deve conter as mesmas funcionalidades que existem no software Efact que está sendo locado pelo período de um ano.</t>
   </si>
   <si>
     <t>Guilherme Mendes</t>
@@ -270,229 +402,187 @@
     <t>Sistemas</t>
   </si>
   <si>
-    <t>05/03/2026</t>
-  </si>
-  <si>
-    <t>28496</t>
-  </si>
-  <si>
-    <t>NOVO LOCAL DE EMPRÉSTIMO</t>
-  </si>
-  <si>
-    <t>27808</t>
-  </si>
-  <si>
-    <t>Ajustes no sistema de ensaios destrutivos de peças seriadas</t>
-  </si>
-  <si>
-    <t>28581</t>
-  </si>
-  <si>
-    <t>Apontamento Inspeção</t>
-  </si>
-  <si>
-    <t>28494</t>
-  </si>
-  <si>
-    <t>Ajuste da tela de Check list de liberação</t>
-  </si>
-  <si>
-    <t>28478</t>
-  </si>
-  <si>
-    <t>Correção de importação</t>
-  </si>
-  <si>
-    <t>27886</t>
-  </si>
-  <si>
-    <t>Registro de inspeção</t>
-  </si>
-  <si>
-    <t>28423</t>
-  </si>
-  <si>
-    <t>Liberar Inventários no Almoxarifado</t>
-  </si>
-  <si>
-    <t>28445</t>
-  </si>
-  <si>
-    <t>ACRESCENTAR COLUNAS SETOR E CABINES APLICAÇÃO APONTAMENTO ACABAMENTO</t>
-  </si>
-  <si>
-    <t>28434</t>
-  </si>
-  <si>
-    <t>Atualizar o banco de dados dos procedimentos de embalagem</t>
-  </si>
-  <si>
-    <t>28289</t>
-  </si>
-  <si>
-    <t>Altona || Sistema ERP || Exportação Requisição OSI</t>
-  </si>
-  <si>
-    <t>28421</t>
-  </si>
-  <si>
-    <t>REGRA FLUXO 108</t>
-  </si>
-  <si>
-    <t>Importar Planilha Tempos da Moldagem</t>
-  </si>
-  <si>
-    <t>26510</t>
-  </si>
-  <si>
-    <t>PROEX Financeiro (Sinalizar Status PROEX)</t>
-  </si>
-  <si>
-    <t>28586</t>
-  </si>
-  <si>
-    <t>Apontamentos Manipulador Rebarbação VI</t>
-  </si>
-  <si>
-    <t>PDI_CheckList - Botão para concluir e liberar o check list</t>
-  </si>
-  <si>
-    <t>22996</t>
-  </si>
-  <si>
-    <t>Habilitar o sistema de apontamento dos manipuladores para o acabamento</t>
-  </si>
-  <si>
-    <t>Criação de sistema que consolide as informações de operação dos equipamentos da fábrica, para cálculo de IROG (Índice de rendimento operacional global). O sistema deve conter as mesmas funcionalidades que existem no software Efact que está sendo locado pelo período de um ano.</t>
+    <t>7727794114</t>
   </si>
   <si>
     <t>PDI_CheckListHeader - Grid com documentos incluídos</t>
   </si>
   <si>
+    <t>7727798373</t>
+  </si>
+  <si>
     <t>PDI_Selecao - Incluir filtro por seleção.</t>
   </si>
   <si>
-    <t>28379</t>
+    <t>7714960095</t>
   </si>
   <si>
     <t>Apontamento Horímetro Deltractor</t>
   </si>
   <si>
+    <t>7727802806</t>
+  </si>
+  <si>
     <t>PDI_Selecao - Retirar do grid Modelo 2 e desenho 2.</t>
   </si>
   <si>
+    <t>7727812644</t>
+  </si>
+  <si>
     <t>PDI_Sequencias - Destacar a opção para exclusão.</t>
   </si>
   <si>
+    <t>7727821848</t>
+  </si>
+  <si>
     <t>PDI_Sequencias - Destacar a mensagem de inclusão em duplicidade.</t>
   </si>
   <si>
+    <t>7727859470</t>
+  </si>
+  <si>
     <t>PDI_RespostaNew - Ocultar o botão "Movimentar aprovadas".</t>
   </si>
   <si>
+    <t>7727868539</t>
+  </si>
+  <si>
     <t>PDI_RespostaNew - Incluir opção para visualizar os documentos anexados.</t>
   </si>
   <si>
+    <t>31/10/2024</t>
+  </si>
+  <si>
+    <t>7728304405</t>
+  </si>
+  <si>
     <t>PDI_Sequencias - Bloquear sequências que estão sem modelo no cadastro</t>
   </si>
   <si>
-    <t>28348</t>
+    <t>7723671928</t>
   </si>
   <si>
     <t>Alterações Sistema Indicadores GIQ - Página inicial - Disponibilizar filtro/opções para alterar o setor dos gráficos</t>
   </si>
   <si>
-    <t>28482</t>
+    <t>7714811699</t>
   </si>
   <si>
     <t>Relatório Faturamento por Sequência (Out/23 a Set/24</t>
   </si>
   <si>
+    <t>7723671973</t>
+  </si>
+  <si>
     <t>Alterações Sistema Indicadores GIQ - Página Inicial -  Disponibilizar gráficos na página inicial de acordo com a área do usuário logado,</t>
   </si>
   <si>
+    <t>7723674699</t>
+  </si>
+  <si>
     <t>Alterações Sistema Indicadores GIQ - Página inicial - Ao clicar no nome do indicador levar para o gráfico correspondente</t>
   </si>
   <si>
+    <t>7723672013</t>
+  </si>
+  <si>
     <t>Alterações Sistema Indicadores GIQ - Página inicial - incluir sinaleiro de acordo com o resultado do indicador no acumulado do ano</t>
   </si>
   <si>
-    <t>28135</t>
+    <t>7723702585</t>
   </si>
   <si>
     <t>Apontamento de moldagem USE - Máquina</t>
   </si>
   <si>
-    <t>24746</t>
+    <t>7724070243</t>
   </si>
   <si>
     <t>Estratificação eventos para Financeiro</t>
   </si>
   <si>
+    <t>10/11/2024</t>
+  </si>
+  <si>
+    <t>7751904391</t>
+  </si>
+  <si>
     <t>Alterar cores da Legenda no plano de ação para "na meta" = Amarelo | "Abaixo da meta" = Vermelho, independentemente de ter ou não plano de ação, de modo que seja mantido o padrão de cores da planilha atual</t>
   </si>
   <si>
-    <t>31/10/2024</t>
-  </si>
-  <si>
     <t>Semana 5</t>
   </si>
   <si>
+    <t>7751907367</t>
+  </si>
+  <si>
     <t>Incluir gráfico do histórico dos anos anteriores na tela inicial. Cor azul escuro</t>
   </si>
   <si>
+    <t>01/11/2024</t>
+  </si>
+  <si>
+    <t>7751911050</t>
+  </si>
+  <si>
     <t>Incluir na tela principal, abaixo do gráfico, a folha de dados dos panos de ação</t>
   </si>
   <si>
+    <t>7751913295</t>
+  </si>
+  <si>
     <t>Alterar as cores do gráfico para azul claro no ano atual e anos anteriores azul escuro</t>
   </si>
   <si>
+    <t>7751916263</t>
+  </si>
+  <si>
     <t>Incluir matricula do responsável no cadastro do indicador</t>
   </si>
   <si>
+    <t>7751918583</t>
+  </si>
+  <si>
     <t>Incluir matricula do responsável por cadastrar a informação</t>
   </si>
   <si>
+    <t>7763739309</t>
+  </si>
+  <si>
     <t>‘SISTEMA PROEX - NOTA PROMISSÓRIA”</t>
   </si>
   <si>
-    <t>01/11/2024</t>
-  </si>
-  <si>
     <t>Semana 1</t>
   </si>
   <si>
     <t>Novembro</t>
   </si>
   <si>
+    <t>7773869628</t>
+  </si>
+  <si>
     <t>Colocar a coluna do acumulado de 2024 dentro do gráfico após o mês de dezembro e, com isso, retirar a coluna de meta, pois no gráfico a meta já está representada pela linha</t>
   </si>
   <si>
-    <t>04/11/2024</t>
-  </si>
-  <si>
-    <t>28708</t>
+    <t>7783852833</t>
   </si>
   <si>
     <t>Ajuste no sistema BLOCO K</t>
   </si>
   <si>
-    <t>05/11/2024</t>
-  </si>
-  <si>
     <t>7686305057</t>
   </si>
   <si>
     <t>Migrar aplicação PID para Gx16 - Interface</t>
   </si>
   <si>
-    <t>28396</t>
+    <t>7714909697</t>
   </si>
   <si>
     <t>Desenvolver Aplicação Qlik Sense - Peso por Macroprocesso</t>
   </si>
   <si>
-    <t>28422</t>
+    <t>7714877160</t>
   </si>
   <si>
     <t>Saldo OC 334307</t>
@@ -504,7 +594,7 @@
     <t>Período</t>
   </si>
   <si>
-    <t>SPRINT 2024-48</t>
+    <t>Out/2024</t>
   </si>
   <si>
     <t>Base</t>
@@ -1140,13 +1230,13 @@
         <v>32</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N3" s="2" t="s">
         <v>27</v>
@@ -1157,37 +1247,37 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J4" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J4" s="2" t="s">
+      <c r="K4" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>25</v>
@@ -1234,13 +1324,13 @@
         <v>32</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N5" s="2" t="s">
         <v>27</v>
@@ -1251,7 +1341,7 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>16</v>
@@ -1263,10 +1353,10 @@
         <v>18</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>31</v>
@@ -1278,10 +1368,10 @@
         <v>22</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>25</v>
@@ -1298,7 +1388,7 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>16</v>
@@ -1310,10 +1400,10 @@
         <v>18</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>31</v>
@@ -1328,13 +1418,13 @@
         <v>32</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N7" s="2" t="s">
         <v>27</v>
@@ -1345,7 +1435,7 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>16</v>
@@ -1357,10 +1447,10 @@
         <v>18</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>31</v>
@@ -1392,7 +1482,7 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>16</v>
@@ -1404,10 +1494,10 @@
         <v>18</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>31</v>
@@ -1422,13 +1512,13 @@
         <v>32</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N9" s="2" t="s">
         <v>27</v>
@@ -1439,22 +1529,22 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>31</v>
@@ -1466,10 +1556,10 @@
         <v>22</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>25</v>
@@ -1486,7 +1576,7 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>16</v>
@@ -1498,10 +1588,10 @@
         <v>18</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>31</v>
@@ -1516,13 +1606,13 @@
         <v>32</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N11" s="2" t="s">
         <v>27</v>
@@ -1533,7 +1623,7 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>16</v>
@@ -1545,10 +1635,10 @@
         <v>18</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>31</v>
@@ -1560,16 +1650,16 @@
         <v>22</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N12" s="2" t="s">
         <v>38</v>
@@ -1580,7 +1670,7 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>16</v>
@@ -1592,10 +1682,10 @@
         <v>18</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>31</v>
@@ -1610,13 +1700,13 @@
         <v>32</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N13" s="2" t="s">
         <v>27</v>
@@ -1627,7 +1717,7 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>16</v>
@@ -1639,10 +1729,10 @@
         <v>18</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>31</v>
@@ -1654,13 +1744,13 @@
         <v>22</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="M14" s="2" t="s">
         <v>26</v>
@@ -1674,7 +1764,7 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>16</v>
@@ -1686,10 +1776,10 @@
         <v>18</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>31</v>
@@ -1704,13 +1794,13 @@
         <v>32</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N15" s="2" t="s">
         <v>27</v>
@@ -1721,7 +1811,7 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>16</v>
@@ -1733,10 +1823,10 @@
         <v>18</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>31</v>
@@ -1748,13 +1838,13 @@
         <v>22</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="M16" s="2" t="s">
         <v>26</v>
@@ -1768,22 +1858,22 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>20</v>
@@ -1798,13 +1888,13 @@
         <v>32</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N17" s="2" t="s">
         <v>27</v>
@@ -1815,7 +1905,7 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>16</v>
@@ -1827,10 +1917,10 @@
         <v>18</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>31</v>
@@ -1842,13 +1932,13 @@
         <v>22</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="M18" s="2" t="s">
         <v>26</v>
@@ -1862,7 +1952,7 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>16</v>
@@ -1874,10 +1964,10 @@
         <v>18</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>31</v>
@@ -1889,13 +1979,13 @@
         <v>22</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="M19" s="2" t="s">
         <v>26</v>
@@ -1909,7 +1999,7 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>16</v>
@@ -1921,10 +2011,10 @@
         <v>18</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>31</v>
@@ -1936,13 +2026,13 @@
         <v>22</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="M20" s="2" t="s">
         <v>26</v>
@@ -1956,7 +2046,7 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>16</v>
@@ -1968,10 +2058,10 @@
         <v>18</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>31</v>
@@ -1983,13 +2073,13 @@
         <v>22</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>24</v>
+        <v>85</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="M21" s="2" t="s">
         <v>26</v>
@@ -2003,7 +2093,7 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>16</v>
@@ -2015,10 +2105,10 @@
         <v>18</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>31</v>
@@ -2030,13 +2120,13 @@
         <v>22</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="M22" s="2" t="s">
         <v>26</v>
@@ -2050,7 +2140,7 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>16</v>
@@ -2059,31 +2149,31 @@
         <v>17</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>84</v>
+        <v>22</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>32</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="M23" s="2" t="s">
         <v>26</v>
@@ -2097,7 +2187,7 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>16</v>
@@ -2109,10 +2199,10 @@
         <v>18</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>31</v>
@@ -2124,13 +2214,13 @@
         <v>22</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K24" s="2" t="s">
         <v>24</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="M24" s="2" t="s">
         <v>26</v>
@@ -2144,7 +2234,7 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>16</v>
@@ -2156,10 +2246,10 @@
         <v>18</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>31</v>
@@ -2174,10 +2264,10 @@
         <v>32</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="M25" s="2" t="s">
         <v>26</v>
@@ -2191,7 +2281,7 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>16</v>
@@ -2203,10 +2293,10 @@
         <v>18</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>31</v>
@@ -2218,13 +2308,13 @@
         <v>22</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="M26" s="2" t="s">
         <v>26</v>
@@ -2238,7 +2328,7 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>16</v>
@@ -2250,10 +2340,10 @@
         <v>18</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>31</v>
@@ -2265,13 +2355,13 @@
         <v>22</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>24</v>
+        <v>85</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="M27" s="2" t="s">
         <v>26</v>
@@ -2285,7 +2375,7 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>16</v>
@@ -2297,10 +2387,10 @@
         <v>18</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>31</v>
@@ -2312,13 +2402,13 @@
         <v>22</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="M28" s="2" t="s">
         <v>26</v>
@@ -2332,7 +2422,7 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>16</v>
@@ -2344,10 +2434,10 @@
         <v>18</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>31</v>
@@ -2362,10 +2452,10 @@
         <v>32</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>24</v>
+        <v>102</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="M29" s="2" t="s">
         <v>26</v>
@@ -2379,7 +2469,7 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>16</v>
@@ -2391,10 +2481,10 @@
         <v>18</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>31</v>
@@ -2406,13 +2496,13 @@
         <v>22</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K30" s="2" t="s">
         <v>24</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="M30" s="2" t="s">
         <v>26</v>
@@ -2426,7 +2516,7 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>16</v>
@@ -2438,10 +2528,10 @@
         <v>18</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>31</v>
@@ -2453,13 +2543,13 @@
         <v>22</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="M31" s="2" t="s">
         <v>26</v>
@@ -2473,7 +2563,7 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>16</v>
@@ -2485,10 +2575,10 @@
         <v>18</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>31</v>
@@ -2500,13 +2590,13 @@
         <v>22</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="M32" s="2" t="s">
         <v>26</v>
@@ -2520,7 +2610,7 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>16</v>
@@ -2532,10 +2622,10 @@
         <v>18</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>31</v>
@@ -2547,13 +2637,13 @@
         <v>22</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>24</v>
+        <v>102</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="M33" s="2" t="s">
         <v>26</v>
@@ -2567,7 +2657,7 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>16</v>
@@ -2579,10 +2669,10 @@
         <v>18</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>31</v>
@@ -2594,13 +2684,13 @@
         <v>22</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="M34" s="2" t="s">
         <v>26</v>
@@ -2614,7 +2704,7 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>35</v>
+        <v>113</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>16</v>
@@ -2626,10 +2716,10 @@
         <v>18</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>20</v>
@@ -2644,10 +2734,10 @@
         <v>32</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="M35" s="2" t="s">
         <v>26</v>
@@ -2661,7 +2751,7 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>16</v>
@@ -2673,10 +2763,10 @@
         <v>18</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>31</v>
@@ -2697,7 +2787,7 @@
         <v>33</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N36" s="2" t="s">
         <v>27</v>
@@ -2708,7 +2798,7 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>16</v>
@@ -2720,10 +2810,10 @@
         <v>18</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>31</v>
@@ -2735,16 +2825,16 @@
         <v>22</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N37" s="2" t="s">
         <v>27</v>
@@ -2755,7 +2845,7 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>57</v>
+        <v>119</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>16</v>
@@ -2767,10 +2857,10 @@
         <v>18</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>31</v>
@@ -2785,10 +2875,10 @@
         <v>32</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>24</v>
+        <v>121</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="M38" s="2" t="s">
         <v>26</v>
@@ -2802,43 +2892,43 @@
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>16</v>
+        <v>123</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>80</v>
+        <v>124</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>31</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>83</v>
+        <v>127</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>84</v>
+        <v>128</v>
       </c>
       <c r="J39" s="2" t="s">
         <v>32</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="L39" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N39" s="2" t="s">
         <v>27</v>
@@ -2849,7 +2939,7 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>57</v>
+        <v>129</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>16</v>
@@ -2861,10 +2951,10 @@
         <v>18</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>31</v>
@@ -2879,10 +2969,10 @@
         <v>32</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="M40" s="2" t="s">
         <v>26</v>
@@ -2896,7 +2986,7 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>57</v>
+        <v>131</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>16</v>
@@ -2908,10 +2998,10 @@
         <v>18</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>31</v>
@@ -2926,10 +3016,10 @@
         <v>32</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="M41" s="2" t="s">
         <v>26</v>
@@ -2943,7 +3033,7 @@
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>16</v>
@@ -2955,10 +3045,10 @@
         <v>18</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>31</v>
@@ -2970,16 +3060,16 @@
         <v>22</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N42" s="2" t="s">
         <v>27</v>
@@ -2990,7 +3080,7 @@
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>57</v>
+        <v>135</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>16</v>
@@ -3002,10 +3092,10 @@
         <v>18</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>121</v>
+        <v>136</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>121</v>
+        <v>136</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>31</v>
@@ -3020,10 +3110,10 @@
         <v>32</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="M43" s="2" t="s">
         <v>26</v>
@@ -3037,7 +3127,7 @@
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>57</v>
+        <v>137</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>16</v>
@@ -3049,10 +3139,10 @@
         <v>18</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>31</v>
@@ -3067,10 +3157,10 @@
         <v>32</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="M44" s="2" t="s">
         <v>26</v>
@@ -3084,7 +3174,7 @@
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>57</v>
+        <v>139</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>16</v>
@@ -3096,10 +3186,10 @@
         <v>18</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>31</v>
@@ -3114,10 +3204,10 @@
         <v>32</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="M45" s="2" t="s">
         <v>26</v>
@@ -3131,7 +3221,7 @@
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>57</v>
+        <v>141</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>16</v>
@@ -3143,10 +3233,10 @@
         <v>18</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>124</v>
+        <v>142</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>124</v>
+        <v>142</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>31</v>
@@ -3161,10 +3251,10 @@
         <v>32</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="M46" s="2" t="s">
         <v>26</v>
@@ -3178,7 +3268,7 @@
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>57</v>
+        <v>143</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>16</v>
@@ -3190,10 +3280,10 @@
         <v>18</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>125</v>
+        <v>144</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>125</v>
+        <v>144</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>31</v>
@@ -3208,10 +3298,10 @@
         <v>32</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>24</v>
+        <v>145</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="M47" s="2" t="s">
         <v>26</v>
@@ -3225,7 +3315,7 @@
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>57</v>
+        <v>146</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>16</v>
@@ -3237,10 +3327,10 @@
         <v>18</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>126</v>
+        <v>147</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>126</v>
+        <v>147</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>31</v>
@@ -3255,10 +3345,10 @@
         <v>32</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="M48" s="2" t="s">
         <v>26</v>
@@ -3272,7 +3362,7 @@
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>127</v>
+        <v>148</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>16</v>
@@ -3284,10 +3374,10 @@
         <v>18</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>128</v>
+        <v>149</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>128</v>
+        <v>149</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>31</v>
@@ -3302,10 +3392,10 @@
         <v>32</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="M49" s="2" t="s">
         <v>26</v>
@@ -3319,7 +3409,7 @@
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>16</v>
@@ -3331,10 +3421,10 @@
         <v>18</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>31</v>
@@ -3346,16 +3436,16 @@
         <v>22</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="L50" s="2" t="s">
         <v>33</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N50" s="2" t="s">
         <v>27</v>
@@ -3366,7 +3456,7 @@
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>127</v>
+        <v>152</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>16</v>
@@ -3378,10 +3468,10 @@
         <v>18</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>131</v>
+        <v>153</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>131</v>
+        <v>153</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>31</v>
@@ -3396,10 +3486,10 @@
         <v>32</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="M51" s="2" t="s">
         <v>26</v>
@@ -3413,7 +3503,7 @@
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>127</v>
+        <v>154</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>16</v>
@@ -3425,10 +3515,10 @@
         <v>18</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>132</v>
+        <v>155</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>132</v>
+        <v>155</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>31</v>
@@ -3443,10 +3533,10 @@
         <v>32</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="M52" s="2" t="s">
         <v>26</v>
@@ -3460,7 +3550,7 @@
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>127</v>
+        <v>156</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>16</v>
@@ -3472,10 +3562,10 @@
         <v>18</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>133</v>
+        <v>157</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>133</v>
+        <v>157</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>31</v>
@@ -3490,10 +3580,10 @@
         <v>32</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="M53" s="2" t="s">
         <v>26</v>
@@ -3507,7 +3597,7 @@
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>16</v>
@@ -3519,10 +3609,10 @@
         <v>18</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>31</v>
@@ -3537,13 +3627,13 @@
         <v>32</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N54" s="2" t="s">
         <v>27</v>
@@ -3554,7 +3644,7 @@
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>136</v>
+        <v>160</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>16</v>
@@ -3566,10 +3656,10 @@
         <v>18</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>137</v>
+        <v>161</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>137</v>
+        <v>161</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>31</v>
@@ -3584,7 +3674,7 @@
         <v>32</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>24</v>
+        <v>162</v>
       </c>
       <c r="L55" s="2" t="s">
         <v>25</v>
@@ -3601,7 +3691,7 @@
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>127</v>
+        <v>163</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>16</v>
@@ -3613,10 +3703,10 @@
         <v>18</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>138</v>
+        <v>164</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>138</v>
+        <v>164</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>31</v>
@@ -3628,19 +3718,19 @@
         <v>22</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="M56" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N56" s="2" t="s">
-        <v>140</v>
+        <v>165</v>
       </c>
       <c r="O56" s="2" t="s">
         <v>28</v>
@@ -3648,7 +3738,7 @@
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>127</v>
+        <v>166</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>16</v>
@@ -3660,10 +3750,10 @@
         <v>18</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>141</v>
+        <v>167</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>141</v>
+        <v>167</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>31</v>
@@ -3675,19 +3765,19 @@
         <v>22</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>24</v>
+        <v>168</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="M57" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N57" s="2" t="s">
-        <v>140</v>
+        <v>165</v>
       </c>
       <c r="O57" s="2" t="s">
         <v>28</v>
@@ -3695,7 +3785,7 @@
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>127</v>
+        <v>169</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>16</v>
@@ -3707,10 +3797,10 @@
         <v>18</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>142</v>
+        <v>170</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>142</v>
+        <v>170</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>31</v>
@@ -3722,19 +3812,19 @@
         <v>22</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>24</v>
+        <v>121</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="M58" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N58" s="2" t="s">
-        <v>140</v>
+        <v>165</v>
       </c>
       <c r="O58" s="2" t="s">
         <v>28</v>
@@ -3742,7 +3832,7 @@
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>127</v>
+        <v>171</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>16</v>
@@ -3754,10 +3844,10 @@
         <v>18</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>143</v>
+        <v>172</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>143</v>
+        <v>172</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>31</v>
@@ -3769,19 +3859,19 @@
         <v>22</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>24</v>
+        <v>168</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="M59" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N59" s="2" t="s">
-        <v>140</v>
+        <v>165</v>
       </c>
       <c r="O59" s="2" t="s">
         <v>28</v>
@@ -3789,7 +3879,7 @@
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>127</v>
+        <v>173</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>16</v>
@@ -3801,10 +3891,10 @@
         <v>18</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>144</v>
+        <v>174</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>144</v>
+        <v>174</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>31</v>
@@ -3816,19 +3906,19 @@
         <v>22</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="M60" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N60" s="2" t="s">
-        <v>140</v>
+        <v>165</v>
       </c>
       <c r="O60" s="2" t="s">
         <v>28</v>
@@ -3836,7 +3926,7 @@
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>127</v>
+        <v>175</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>16</v>
@@ -3848,34 +3938,34 @@
         <v>18</v>
       </c>
       <c r="E61" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I61" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J61" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="F61" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="G61" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="H61" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I61" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J61" s="2" t="s">
-        <v>139</v>
-      </c>
       <c r="K61" s="2" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="M61" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N61" s="2" t="s">
-        <v>140</v>
+        <v>165</v>
       </c>
       <c r="O61" s="2" t="s">
         <v>28</v>
@@ -3883,7 +3973,7 @@
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>109</v>
+        <v>177</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>16</v>
@@ -3895,10 +3985,10 @@
         <v>18</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>146</v>
+        <v>178</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>146</v>
+        <v>178</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>31</v>
@@ -3910,27 +4000,27 @@
         <v>22</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>147</v>
+        <v>168</v>
       </c>
       <c r="K62" s="2" t="s">
         <v>24</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="M62" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N62" s="2" t="s">
-        <v>148</v>
+        <v>179</v>
       </c>
       <c r="O62" s="2" t="s">
-        <v>149</v>
+        <v>180</v>
       </c>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>16</v>
@@ -3942,10 +4032,10 @@
         <v>18</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>150</v>
+        <v>182</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>150</v>
+        <v>182</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>31</v>
@@ -3957,27 +4047,27 @@
         <v>22</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>151</v>
+        <v>102</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>24</v>
+        <v>85</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="M63" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N63" s="2" t="s">
-        <v>148</v>
+        <v>179</v>
       </c>
       <c r="O63" s="2" t="s">
-        <v>149</v>
+        <v>180</v>
       </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>152</v>
+        <v>183</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>16</v>
@@ -3989,10 +4079,10 @@
         <v>18</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>153</v>
+        <v>184</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>153</v>
+        <v>184</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>31</v>
@@ -4004,27 +4094,27 @@
         <v>22</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>154</v>
+        <v>85</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>24</v>
+        <v>162</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="M64" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N64" s="2" t="s">
-        <v>148</v>
+        <v>179</v>
       </c>
       <c r="O64" s="2" t="s">
-        <v>149</v>
+        <v>180</v>
       </c>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>155</v>
+        <v>185</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>16</v>
@@ -4036,10 +4126,10 @@
         <v>18</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>156</v>
+        <v>186</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>156</v>
+        <v>186</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>20</v>
@@ -4054,10 +4144,10 @@
         <v>23</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="L65" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="M65" s="2" t="s">
         <v>26</v>
@@ -4071,7 +4161,7 @@
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>157</v>
+        <v>187</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>16</v>
@@ -4083,10 +4173,10 @@
         <v>18</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>158</v>
+        <v>188</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>158</v>
+        <v>188</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>31</v>
@@ -4098,16 +4188,16 @@
         <v>22</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L66" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M66" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N66" s="2" t="s">
         <v>27</v>
@@ -4118,7 +4208,7 @@
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>159</v>
+        <v>189</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>16</v>
@@ -4130,10 +4220,10 @@
         <v>18</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>31</v>
@@ -4145,16 +4235,16 @@
         <v>22</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L67" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M67" s="2" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="N67" s="2" t="s">
         <v>27</v>
@@ -4176,23 +4266,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>161</v>
+        <v>191</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>162</v>
+        <v>192</v>
       </c>
       <c r="B2" t="s">
-        <v>163</v>
+        <v>193</v>
       </c>
       <c r="D2" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="E2" t="s">
-        <v>165</v>
+        <v>195</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -4200,16 +4290,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>166</v>
+        <v>196</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>167</v>
+        <v>197</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>168</v>
+        <v>198</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>169</v>
+        <v>199</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -4220,20 +4310,20 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <v>494</v>
+        <v>8.33</v>
       </c>
       <c r="J5" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>170</v>
+        <v>200</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J22" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="K22">
         <v>43</v>
@@ -4249,7 +4339,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>171</v>
+        <v>201</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -4280,12 +4370,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>172</v>
+        <v>202</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>166</v>
+        <v>196</v>
       </c>
       <c r="B2">
         <v>66</v>
@@ -4299,35 +4389,35 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>494</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>173</v>
+        <v>203</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>174</v>
+        <v>204</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>176</v>
+        <v>206</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>177</v>
+        <v>207</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>178</v>
+        <v>208</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -4335,7 +4425,7 @@
         <v>16</v>
       </c>
       <c r="B10">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D10" t="s">
         <v>17</v>
@@ -4344,33 +4434,39 @@
         <v>63</v>
       </c>
       <c r="G10" t="s">
-        <v>179</v>
+        <v>209</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="K10">
         <v>0</v>
       </c>
       <c r="M10" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="N10">
         <v>43</v>
       </c>
       <c r="P10" t="s">
-        <v>148</v>
+        <v>179</v>
       </c>
       <c r="Q10">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="4:17" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>123</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
       <c r="D11" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="E11">
         <v>2</v>
@@ -4385,10 +4481,10 @@
         <v>26</v>
       </c>
       <c r="K11">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="M11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="N11">
         <v>11</v>
@@ -4397,12 +4493,12 @@
         <v>38</v>
       </c>
       <c r="Q11">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D12" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -4414,13 +4510,13 @@
         <v>61</v>
       </c>
       <c r="J12" t="s">
-        <v>181</v>
+        <v>211</v>
       </c>
       <c r="K12">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="N12">
         <v>1</v>
@@ -4429,12 +4525,12 @@
         <v>27</v>
       </c>
       <c r="Q12">
-        <v>36</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="7:17" x14ac:dyDescent="0.25">
       <c r="G13" t="s">
-        <v>182</v>
+        <v>212</v>
       </c>
       <c r="H13">
         <v>0</v>
@@ -4446,15 +4542,15 @@
         <v>4</v>
       </c>
       <c r="P13" t="s">
-        <v>140</v>
+        <v>165</v>
       </c>
       <c r="Q13">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
-        <v>183</v>
+        <v>213</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -4468,7 +4564,7 @@
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>184</v>
+        <v>214</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -4476,7 +4572,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>185</v>
+        <v>215</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -4484,7 +4580,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>186</v>
+        <v>216</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -4492,10 +4588,10 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D20" s="1" t="s">
         <v>0</v>
       </c>
@@ -4503,7 +4599,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>188</v>
+        <v>218</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -4511,142 +4607,142 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>79</v>
+        <v>29</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F21" s="2">
-        <v>479</v>
+        <v>600</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>81</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F22" s="2">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F23" s="2">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F24" s="2">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F25" s="2">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F26" s="2">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F27" s="2">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F28" s="2">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F29" s="2">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>71</v>
+        <v>115</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F30" s="2">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>72</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>
